--- a/画面設計/【画面設計】定数一覧.xlsx
+++ b/画面設計/【画面設計】定数一覧.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="128">
   <si>
     <t>アプリ課題(2025）</t>
   </si>
@@ -380,6 +380,27 @@
   </si>
   <si>
     <t>★★★★★</t>
+  </si>
+  <si>
+    <t>性別</t>
+  </si>
+  <si>
+    <t>GENDERLESS</t>
+  </si>
+  <si>
+    <t>未設定</t>
+  </si>
+  <si>
+    <t>GENDER_MAN</t>
+  </si>
+  <si>
+    <t>男性</t>
+  </si>
+  <si>
+    <t>GENDER_WOMAN</t>
+  </si>
+  <si>
+    <t>女性</t>
   </si>
 </sst>
 </file>
@@ -2828,11 +2849,55 @@
       </c>
     </row>
     <row r="71" ht="18.75" customHeight="1"/>
-    <row r="72" ht="18.75" customHeight="1"/>
-    <row r="73" ht="18.75" customHeight="1"/>
-    <row r="74" ht="18.75" customHeight="1"/>
-    <row r="75" ht="18.75" customHeight="1"/>
-    <row r="76" ht="18.75" customHeight="1"/>
+    <row r="72" ht="18.75" customHeight="1">
+      <c r="D72" s="22" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="73" ht="18.75" customHeight="1">
+      <c r="D73" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E73" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F73" s="23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" ht="18.75" customHeight="1">
+      <c r="D74" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="E74" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="F74" s="25" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="75" ht="18.75" customHeight="1">
+      <c r="D75" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="E75" s="25">
+        <v>1.0</v>
+      </c>
+      <c r="F75" s="25" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="76" ht="18.75" customHeight="1">
+      <c r="D76" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E76" s="25">
+        <v>2.0</v>
+      </c>
+      <c r="F76" s="25" t="s">
+        <v>127</v>
+      </c>
+    </row>
     <row r="77" ht="18.75" customHeight="1"/>
     <row r="78" ht="18.75" customHeight="1"/>
     <row r="79" ht="18.75" customHeight="1"/>
